--- a/LTL_qty_updated.xlsx
+++ b/LTL_qty_updated.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://acusa-my.sharepoint.com/personal/g_ghedini_atlasconcordeusa_com/Documents/Desktop/AI - Automations/BOL creation/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="150" documentId="8_{41BA2822-1FC3-424A-BF5C-A2447EBC91C2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3F466C27-1A1D-4CBE-8E92-1B583420E53F}"/>
+  <xr:revisionPtr revIDLastSave="152" documentId="8_{41BA2822-1FC3-424A-BF5C-A2447EBC91C2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9564CA87-EEC7-4CE4-B7AA-E69263C4D10E}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{B388D9E8-F042-4987-BDB7-8E3EC1CFA04A}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{B388D9E8-F042-4987-BDB7-8E3EC1CFA04A}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -2762,7 +2762,7 @@
         <v>22</v>
       </c>
       <c r="D73">
-        <v>16</v>
+        <v>160</v>
       </c>
       <c r="E73">
         <v>70</v>
@@ -2782,7 +2782,7 @@
         <v>23</v>
       </c>
       <c r="D74">
-        <v>16</v>
+        <v>160</v>
       </c>
       <c r="E74">
         <v>70</v>
@@ -2802,7 +2802,7 @@
         <v>24</v>
       </c>
       <c r="D75">
-        <v>16</v>
+        <v>160</v>
       </c>
       <c r="E75">
         <v>70</v>
@@ -2822,7 +2822,7 @@
         <v>25</v>
       </c>
       <c r="D76">
-        <v>16</v>
+        <v>160</v>
       </c>
       <c r="E76">
         <v>70</v>
@@ -2842,7 +2842,7 @@
         <v>26</v>
       </c>
       <c r="D77">
-        <v>16</v>
+        <v>160</v>
       </c>
       <c r="E77">
         <v>70</v>

--- a/LTL_qty_updated.xlsx
+++ b/LTL_qty_updated.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://acusa-my.sharepoint.com/personal/g_ghedini_atlasconcordeusa_com/Documents/Desktop/AI - Automations/BOL creation/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Giovanni Ghedini\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="152" documentId="8_{41BA2822-1FC3-424A-BF5C-A2447EBC91C2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9564CA87-EEC7-4CE4-B7AA-E69263C4D10E}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F88C145B-D7CF-4402-A9A6-23C7693AE3DD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{B388D9E8-F042-4987-BDB7-8E3EC1CFA04A}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$E$130</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$E$163</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="444" uniqueCount="152">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="492" uniqueCount="168">
   <si>
     <t>D23_Floor and Wall Tiles</t>
   </si>
@@ -864,6 +864,54 @@
   </si>
   <si>
     <t>TN</t>
+  </si>
+  <si>
+    <t>Travertine Almond Matte 12x24</t>
+  </si>
+  <si>
+    <t>Travertine Light Matte 24x48</t>
+  </si>
+  <si>
+    <t>Pietra Limestone Clay 12x24</t>
+  </si>
+  <si>
+    <t>Pietra Limestone Silver 12x24</t>
+  </si>
+  <si>
+    <t>Urban White &amp; Ash Checkerboard Mosaic 11.75x11.75</t>
+  </si>
+  <si>
+    <t>Urban Sand 12x24</t>
+  </si>
+  <si>
+    <t>Urban Gray 12x24</t>
+  </si>
+  <si>
+    <t>Urban Smoke 12x24</t>
+  </si>
+  <si>
+    <t>Slate Gray 12x24</t>
+  </si>
+  <si>
+    <t>Slate Beige 12x24</t>
+  </si>
+  <si>
+    <t>Urban Jade Evo Mosaic 11.75x11.75</t>
+  </si>
+  <si>
+    <t>Slate Midnight Linear Mosaic 11.75x11.75</t>
+  </si>
+  <si>
+    <t>Slate Black Linear Mosaic 11.75x11.75</t>
+  </si>
+  <si>
+    <t>Impero Travertine 24x24</t>
+  </si>
+  <si>
+    <t>Selva Brown 24x24</t>
+  </si>
+  <si>
+    <t>Impero Dolomite 24x24</t>
   </si>
 </sst>
 </file>
@@ -1018,7 +1066,17 @@
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="1">
+  <dxfs count="2">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -1040,10 +1098,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1363,7 +1417,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F30446A3-A986-4686-A765-4C12AB9F4FB1}">
-  <dimension ref="A1:F147"/>
+  <dimension ref="A1:F163"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="15.6640625" bestFit="1" customWidth="1"/>
@@ -3324,8 +3378,8 @@
       <c r="D101">
         <v>8</v>
       </c>
-      <c r="E101" t="e">
-        <v>#N/A</v>
+      <c r="E101">
+        <v>36</v>
       </c>
       <c r="F101" t="s">
         <v>151</v>
@@ -4239,10 +4293,330 @@
         <v>147</v>
       </c>
     </row>
+    <row r="148" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A148" t="s">
+        <v>29</v>
+      </c>
+      <c r="B148" s="2">
+        <v>610010006071</v>
+      </c>
+      <c r="C148" t="s">
+        <v>152</v>
+      </c>
+      <c r="D148">
+        <v>5</v>
+      </c>
+      <c r="E148">
+        <v>32</v>
+      </c>
+      <c r="F148" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="149" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A149" t="s">
+        <v>29</v>
+      </c>
+      <c r="B149" s="2">
+        <v>610010006101</v>
+      </c>
+      <c r="C149" t="s">
+        <v>153</v>
+      </c>
+      <c r="E149">
+        <v>35</v>
+      </c>
+      <c r="F149" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="150" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A150" t="s">
+        <v>29</v>
+      </c>
+      <c r="B150" s="2">
+        <v>610010005779</v>
+      </c>
+      <c r="C150" t="s">
+        <v>154</v>
+      </c>
+      <c r="D150">
+        <v>5</v>
+      </c>
+      <c r="E150">
+        <v>32</v>
+      </c>
+      <c r="F150" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="151" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A151" t="s">
+        <v>29</v>
+      </c>
+      <c r="B151" s="2">
+        <v>610010005781</v>
+      </c>
+      <c r="C151" t="s">
+        <v>155</v>
+      </c>
+      <c r="D151">
+        <v>5</v>
+      </c>
+      <c r="E151">
+        <v>32</v>
+      </c>
+      <c r="F151" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="152" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A152" t="s">
+        <v>29</v>
+      </c>
+      <c r="B152" s="2">
+        <v>610110001491</v>
+      </c>
+      <c r="C152" t="s">
+        <v>156</v>
+      </c>
+      <c r="D152">
+        <v>7</v>
+      </c>
+      <c r="E152">
+        <v>36</v>
+      </c>
+      <c r="F152" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="153" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A153" t="s">
+        <v>29</v>
+      </c>
+      <c r="B153" s="2">
+        <v>610010005273</v>
+      </c>
+      <c r="C153" t="s">
+        <v>157</v>
+      </c>
+      <c r="D153">
+        <v>5</v>
+      </c>
+      <c r="E153">
+        <v>32</v>
+      </c>
+      <c r="F153" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="154" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A154" t="s">
+        <v>29</v>
+      </c>
+      <c r="B154" s="2">
+        <v>610010005276</v>
+      </c>
+      <c r="C154" t="s">
+        <v>158</v>
+      </c>
+      <c r="D154">
+        <v>5</v>
+      </c>
+      <c r="E154">
+        <v>32</v>
+      </c>
+      <c r="F154" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="155" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A155" t="s">
+        <v>29</v>
+      </c>
+      <c r="B155" s="2">
+        <v>610010005277</v>
+      </c>
+      <c r="C155" t="s">
+        <v>159</v>
+      </c>
+      <c r="D155">
+        <v>5</v>
+      </c>
+      <c r="E155">
+        <v>32</v>
+      </c>
+      <c r="F155" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="156" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A156" t="s">
+        <v>29</v>
+      </c>
+      <c r="B156" s="2">
+        <v>610010005269</v>
+      </c>
+      <c r="C156" t="s">
+        <v>160</v>
+      </c>
+      <c r="D156">
+        <v>5</v>
+      </c>
+      <c r="E156">
+        <v>32</v>
+      </c>
+      <c r="F156" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="157" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A157" t="s">
+        <v>29</v>
+      </c>
+      <c r="B157" s="2">
+        <v>610010005267</v>
+      </c>
+      <c r="C157" t="s">
+        <v>161</v>
+      </c>
+      <c r="D157">
+        <v>5</v>
+      </c>
+      <c r="E157">
+        <v>32</v>
+      </c>
+      <c r="F157" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="158" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A158" t="s">
+        <v>29</v>
+      </c>
+      <c r="B158" s="2">
+        <v>610110000995</v>
+      </c>
+      <c r="C158" t="s">
+        <v>162</v>
+      </c>
+      <c r="D158">
+        <v>7</v>
+      </c>
+      <c r="E158">
+        <v>36</v>
+      </c>
+      <c r="F158" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="159" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A159" t="s">
+        <v>29</v>
+      </c>
+      <c r="B159" s="2">
+        <v>610110001007</v>
+      </c>
+      <c r="C159" t="s">
+        <v>163</v>
+      </c>
+      <c r="D159">
+        <v>7</v>
+      </c>
+      <c r="E159">
+        <v>36</v>
+      </c>
+      <c r="F159" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="160" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A160" t="s">
+        <v>29</v>
+      </c>
+      <c r="B160" s="2">
+        <v>610110001008</v>
+      </c>
+      <c r="C160" t="s">
+        <v>164</v>
+      </c>
+      <c r="D160">
+        <v>7</v>
+      </c>
+      <c r="E160">
+        <v>36</v>
+      </c>
+      <c r="F160" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="161" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A161" t="s">
+        <v>30</v>
+      </c>
+      <c r="B161" s="2">
+        <v>610010005930</v>
+      </c>
+      <c r="C161" t="s">
+        <v>165</v>
+      </c>
+      <c r="D161">
+        <v>4</v>
+      </c>
+      <c r="E161">
+        <v>60</v>
+      </c>
+      <c r="F161" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="162" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A162" t="s">
+        <v>30</v>
+      </c>
+      <c r="B162" s="2">
+        <v>610010005931</v>
+      </c>
+      <c r="C162" t="s">
+        <v>166</v>
+      </c>
+      <c r="D162">
+        <v>4</v>
+      </c>
+      <c r="E162">
+        <v>60</v>
+      </c>
+      <c r="F162" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="163" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A163" t="s">
+        <v>30</v>
+      </c>
+      <c r="B163" s="2">
+        <v>610010006327</v>
+      </c>
+      <c r="C163" t="s">
+        <v>167</v>
+      </c>
+      <c r="D163">
+        <v>4</v>
+      </c>
+      <c r="E163">
+        <v>60</v>
+      </c>
+      <c r="F163" t="s">
+        <v>151</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E130" xr:uid="{F30446A3-A986-4686-A765-4C12AB9F4FB1}"/>
+  <autoFilter ref="A1:E163" xr:uid="{F30446A3-A986-4686-A765-4C12AB9F4FB1}"/>
   <conditionalFormatting sqref="B2:B144">
-    <cfRule type="duplicateValues" dxfId="0" priority="10"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="11"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B148:B149 B153:B154 B158:B159 B163">
+    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
   </conditionalFormatting>
   <hyperlinks>
     <hyperlink ref="C10" r:id="rId1" xr:uid="{89506ED6-C4FD-47B8-9FD6-878DCA92E9AA}"/>
